--- a/xiuxian配置表/yunxing_params/z_moni.xlsx
+++ b/xiuxian配置表/yunxing_params/z_moni.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="64">
   <si>
     <t>键</t>
   </si>
@@ -193,13 +193,13 @@
     <t>item_slots</t>
   </si>
   <si>
-    <t>["",""]</t>
+    <t>["","",""]</t>
   </si>
   <si>
     <t>equip_slots</t>
   </si>
   <si>
-    <t>[-1,-1]</t>
+    <t>[-1]</t>
   </si>
   <si>
     <t>float</t>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>battle_loss_hp_floor_ratio</t>
+  </si>
+  <si>
+    <t>[-1,-1,-1]</t>
+  </si>
+  <si>
+    <t>support_3</t>
   </si>
 </sst>
 </file>
@@ -859,7 +865,7 @@
         <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>25</v>
@@ -915,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>25</v>
@@ -1298,7 +1304,7 @@
         <v>57</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
